--- a/utils/reference/bpi_cards_xdays-header.xlsx
+++ b/utils/reference/bpi_cards_xdays-header.xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12180"/>
+    <workbookView windowWidth="27945" windowHeight="11460"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$BQ$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$AR$2</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="74">
   <si>
     <t>CUST_ID</t>
   </si>
@@ -38,9 +38,6 @@
     <t>CUST_NAME</t>
   </si>
   <si>
-    <t>QUEUE</t>
-  </si>
-  <si>
     <t>OFC</t>
   </si>
   <si>
@@ -86,15 +83,6 @@
     <t>LAST_PAYMENT_DATE</t>
   </si>
   <si>
-    <t>RESPONSE_CODE</t>
-  </si>
-  <si>
-    <t>LAST_CONTACT_DATE</t>
-  </si>
-  <si>
-    <t>BEHAVIOURAL_SCORE</t>
-  </si>
-  <si>
     <t>DELINQUENCY_STRING</t>
   </si>
   <si>
@@ -104,30 +92,12 @@
     <t>DEBIT_AMOUNT_PREFERENCE</t>
   </si>
   <si>
-    <t>MS</t>
-  </si>
-  <si>
-    <t>DOSRI_FLAG</t>
-  </si>
-  <si>
-    <t>EMPLOYEE_CODE</t>
-  </si>
-  <si>
-    <t>RM_NUMBER</t>
-  </si>
-  <si>
     <t>COLLECTION_CYCLE</t>
   </si>
   <si>
     <t>UNIT_CODE</t>
   </si>
   <si>
-    <t>UNIT_DESC</t>
-  </si>
-  <si>
-    <t>LAST_ACTION_CODE</t>
-  </si>
-  <si>
     <t>RISK</t>
   </si>
   <si>
@@ -143,15 +113,9 @@
     <t>UNIBANKER</t>
   </si>
   <si>
-    <t>NS with tranx</t>
-  </si>
-  <si>
     <t>TPAP</t>
   </si>
   <si>
-    <t>CRISPR</t>
-  </si>
-  <si>
     <t>block_code</t>
   </si>
   <si>
@@ -176,12 +140,6 @@
     <t>Balance Type</t>
   </si>
   <si>
-    <t>HO AMOUNT</t>
-  </si>
-  <si>
-    <t>PRIO LIST</t>
-  </si>
-  <si>
     <t>PTP AMOUNT</t>
   </si>
   <si>
@@ -194,9 +152,6 @@
     <t>TPAP DD</t>
   </si>
   <si>
-    <t>AGENCY</t>
-  </si>
-  <si>
     <t>CLASSIF 2</t>
   </si>
   <si>
@@ -209,63 +164,12 @@
     <t>CATEGORY</t>
   </si>
   <si>
-    <t>SPOUSE NUMBER</t>
-  </si>
-  <si>
-    <t>PTP FROM</t>
-  </si>
-  <si>
-    <t>ADDRESS_1</t>
-  </si>
-  <si>
-    <t>ADDRESS_2</t>
-  </si>
-  <si>
-    <t>ADDRESS_3</t>
-  </si>
-  <si>
-    <t>ADEPTRA RESULT</t>
-  </si>
-  <si>
-    <t>USER_FLG8</t>
-  </si>
-  <si>
-    <t>P_RESON_CD</t>
-  </si>
-  <si>
-    <t>TP_PDR_Code</t>
-  </si>
-  <si>
-    <t>EMPLOYMENT</t>
-  </si>
-  <si>
-    <t>EXCLUSION</t>
-  </si>
-  <si>
-    <t>PREDEL NOTIF</t>
-  </si>
-  <si>
-    <t>PUSHBACK STAT</t>
-  </si>
-  <si>
-    <t>ACQUISITION CHANNEL</t>
-  </si>
-  <si>
-    <t>OCCUPATION</t>
-  </si>
-  <si>
-    <t>TYPE</t>
-  </si>
-  <si>
     <t>CUST ID</t>
   </si>
   <si>
     <t>Customer Name</t>
   </si>
   <si>
-    <t>Queue Code</t>
-  </si>
-  <si>
     <t>OFFICE_PH</t>
   </si>
   <si>
@@ -299,24 +203,15 @@
     <t>Last Payment Date</t>
   </si>
   <si>
-    <t>LCD</t>
-  </si>
-  <si>
     <t>ADA ACCT</t>
   </si>
   <si>
     <t>DAP</t>
   </si>
   <si>
-    <t>MARKET_SEGMENT</t>
-  </si>
-  <si>
     <t>Unit Code</t>
   </si>
   <si>
-    <t>Last Action Code</t>
-  </si>
-  <si>
     <t>TPAP CLASSIF</t>
   </si>
   <si>
@@ -336,24 +231,6 @@
   </si>
   <si>
     <t>PTP AMT</t>
-  </si>
-  <si>
-    <t>Address 1</t>
-  </si>
-  <si>
-    <t>Address 2</t>
-  </si>
-  <si>
-    <t>Address 3</t>
-  </si>
-  <si>
-    <t>ref_channel</t>
-  </si>
-  <si>
-    <t>Occupation</t>
-  </si>
-  <si>
-    <t>process_type</t>
   </si>
   <si>
     <t>Amount_Overdue</t>
@@ -1007,7 +884,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1057,12 +934,6 @@
     </xf>
     <xf numFmtId="1" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1607,96 +1478,68 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:BW6"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="5"/>
+  <dimension ref="A1:AR5"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="4"/>
   <cols>
     <col min="1" max="1" width="8.42857142857143" customWidth="1"/>
     <col min="2" max="2" width="15.4285714285714" customWidth="1"/>
-    <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="10.5714285714286" customWidth="1"/>
-    <col min="5" max="5" width="9.85714285714286" customWidth="1"/>
-    <col min="6" max="6" width="11.7142857142857" customWidth="1"/>
-    <col min="7" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
-    <col min="9" max="9" width="6.57142857142857" customWidth="1"/>
-    <col min="10" max="10" width="8.28571428571429" customWidth="1"/>
-    <col min="11" max="11" width="12.8571428571429" customWidth="1"/>
-    <col min="12" max="12" width="23.5714285714286" customWidth="1"/>
-    <col min="13" max="13" width="7.71428571428571" customWidth="1"/>
-    <col min="14" max="14" width="18.8571428571429" customWidth="1"/>
-    <col min="15" max="15" width="18.7142857142857" customWidth="1"/>
-    <col min="16" max="16" width="6.71428571428571" customWidth="1"/>
-    <col min="17" max="17" width="23.7142857142857" customWidth="1"/>
-    <col min="18" max="18" width="20.8571428571429" customWidth="1"/>
-    <col min="19" max="19" width="16.1428571428571" customWidth="1"/>
-    <col min="20" max="20" width="20.4285714285714" customWidth="1"/>
-    <col min="21" max="21" width="20.7142857142857" customWidth="1"/>
-    <col min="22" max="22" width="21.7142857142857" customWidth="1"/>
-    <col min="23" max="23" width="14.8571428571429" customWidth="1"/>
-    <col min="24" max="24" width="28" customWidth="1"/>
-    <col min="25" max="25" width="18" customWidth="1"/>
-    <col min="26" max="26" width="12" customWidth="1"/>
-    <col min="27" max="27" width="16.4285714285714" customWidth="1"/>
-    <col min="28" max="28" width="13.1428571428571" customWidth="1"/>
-    <col min="29" max="29" width="18.4285714285714" customWidth="1"/>
-    <col min="30" max="30" width="11.2857142857143" customWidth="1"/>
-    <col min="31" max="31" width="10.8571428571429" customWidth="1"/>
-    <col min="32" max="32" width="19.1428571428571" customWidth="1"/>
-    <col min="33" max="33" width="4.85714285714286" customWidth="1"/>
-    <col min="34" max="34" width="7.14285714285714" customWidth="1"/>
-    <col min="35" max="35" width="8.71428571428571" customWidth="1"/>
-    <col min="36" max="36" width="10.7142857142857" customWidth="1"/>
-    <col min="37" max="37" width="11.5714285714286" customWidth="1"/>
-    <col min="38" max="39" width="12.8571428571429" customWidth="1"/>
-    <col min="40" max="40" width="7.14285714285714" customWidth="1"/>
-    <col min="41" max="42" width="12" customWidth="1"/>
-    <col min="43" max="43" width="12.8571428571429" customWidth="1"/>
-    <col min="44" max="44" width="11.5714285714286" customWidth="1"/>
-    <col min="45" max="45" width="9.28571428571429" customWidth="1"/>
-    <col min="46" max="46" width="18.5714285714286" customWidth="1"/>
-    <col min="47" max="47" width="23" customWidth="1"/>
-    <col min="48" max="48" width="25.2857142857143" customWidth="1"/>
-    <col min="49" max="49" width="12.5714285714286" customWidth="1"/>
-    <col min="50" max="50" width="9.14285714285714" customWidth="1"/>
-    <col min="51" max="51" width="13.2857142857143" customWidth="1"/>
-    <col min="52" max="52" width="14.5714285714286" customWidth="1"/>
-    <col min="53" max="53" width="15.4285714285714" customWidth="1"/>
-    <col min="54" max="54" width="8.57142857142857" customWidth="1"/>
-    <col min="55" max="55" width="8.42857142857143" customWidth="1"/>
-    <col min="56" max="56" width="9.28571428571429" customWidth="1"/>
-    <col min="57" max="57" width="9.14285714285714" customWidth="1"/>
-    <col min="58" max="58" width="11.4285714285714" customWidth="1"/>
-    <col min="59" max="59" width="10.5714285714286" customWidth="1"/>
-    <col min="60" max="60" width="16.5714285714286" customWidth="1"/>
-    <col min="61" max="61" width="10.1428571428571" customWidth="1"/>
-    <col min="62" max="64" width="11" customWidth="1"/>
-    <col min="65" max="65" width="16.1428571428571" customWidth="1"/>
-    <col min="66" max="66" width="10.8571428571429" customWidth="1"/>
-    <col min="67" max="67" width="12.5714285714286" customWidth="1"/>
-    <col min="68" max="68" width="13.4285714285714" customWidth="1"/>
-    <col min="69" max="69" width="13.8571428571429" customWidth="1"/>
-    <col min="70" max="70" width="11" customWidth="1"/>
-    <col min="71" max="71" width="13.4285714285714" customWidth="1"/>
-    <col min="72" max="72" width="15.4285714285714" customWidth="1"/>
-    <col min="73" max="73" width="22.1428571428571" customWidth="1"/>
-    <col min="74" max="74" width="13.1428571428571" customWidth="1"/>
-    <col min="75" max="75" width="13.2857142857143" customWidth="1"/>
+    <col min="3" max="3" width="10.5714285714286" customWidth="1"/>
+    <col min="4" max="4" width="9.85714285714286" customWidth="1"/>
+    <col min="5" max="5" width="11.7142857142857" customWidth="1"/>
+    <col min="6" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="9" customWidth="1"/>
+    <col min="8" max="8" width="6.57142857142857" customWidth="1"/>
+    <col min="9" max="9" width="8.28571428571429" customWidth="1"/>
+    <col min="10" max="10" width="12.8571428571429" customWidth="1"/>
+    <col min="11" max="11" width="23.5714285714286" customWidth="1"/>
+    <col min="12" max="12" width="7.71428571428571" customWidth="1"/>
+    <col min="13" max="13" width="18.8571428571429" customWidth="1"/>
+    <col min="14" max="14" width="18.7142857142857" customWidth="1"/>
+    <col min="15" max="15" width="6.71428571428571" customWidth="1"/>
+    <col min="16" max="16" width="23.7142857142857" customWidth="1"/>
+    <col min="17" max="17" width="20.8571428571429" customWidth="1"/>
+    <col min="18" max="18" width="21.7142857142857" customWidth="1"/>
+    <col min="19" max="19" width="14.8571428571429" customWidth="1"/>
+    <col min="20" max="20" width="28" customWidth="1"/>
+    <col min="21" max="21" width="18.4285714285714" customWidth="1"/>
+    <col min="22" max="22" width="11.2857142857143" customWidth="1"/>
+    <col min="23" max="23" width="4.85714285714286" customWidth="1"/>
+    <col min="24" max="24" width="7.14285714285714" customWidth="1"/>
+    <col min="25" max="25" width="8.71428571428571" customWidth="1"/>
+    <col min="26" max="26" width="10.7142857142857" customWidth="1"/>
+    <col min="27" max="27" width="11.5714285714286" customWidth="1"/>
+    <col min="28" max="28" width="12.8571428571429" customWidth="1"/>
+    <col min="29" max="30" width="12" customWidth="1"/>
+    <col min="31" max="31" width="12.8571428571429" customWidth="1"/>
+    <col min="32" max="32" width="11.5714285714286" customWidth="1"/>
+    <col min="33" max="33" width="9.28571428571429" customWidth="1"/>
+    <col min="34" max="34" width="18.5714285714286" customWidth="1"/>
+    <col min="35" max="35" width="23" customWidth="1"/>
+    <col min="36" max="36" width="25.2857142857143" customWidth="1"/>
+    <col min="37" max="37" width="13.2857142857143" customWidth="1"/>
+    <col min="38" max="38" width="14.5714285714286" customWidth="1"/>
+    <col min="39" max="39" width="15.4285714285714" customWidth="1"/>
+    <col min="40" max="40" width="8.57142857142857" customWidth="1"/>
+    <col min="41" max="41" width="9.28571428571429" customWidth="1"/>
+    <col min="42" max="42" width="9.14285714285714" customWidth="1"/>
+    <col min="43" max="43" width="11.4285714285714" customWidth="1"/>
+    <col min="44" max="44" width="10.5714285714286" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:75">
+    <row r="1" spans="1:44">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
@@ -1711,7 +1554,7 @@
       <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="1" t="s">
@@ -1732,16 +1575,16 @@
       <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="13" t="s">
+      <c r="R1" s="2" t="s">
         <v>17</v>
       </c>
       <c r="S1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="13" t="s">
+      <c r="T1" s="2" t="s">
         <v>19</v>
       </c>
       <c r="U1" s="2" t="s">
@@ -1759,7 +1602,7 @@
       <c r="Y1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="Z1" s="13" t="s">
         <v>25</v>
       </c>
       <c r="AA1" s="2" t="s">
@@ -1774,10 +1617,10 @@
       <c r="AD1" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="2" t="s">
+      <c r="AE1" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="2" t="s">
+      <c r="AF1" s="16" t="s">
         <v>31</v>
       </c>
       <c r="AG1" s="2" t="s">
@@ -1786,10 +1629,10 @@
       <c r="AH1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="2" t="s">
+      <c r="AI1" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="13" t="s">
+      <c r="AJ1" s="2" t="s">
         <v>35</v>
       </c>
       <c r="AK1" s="2" t="s">
@@ -1810,120 +1653,27 @@
       <c r="AP1" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="AQ1" s="13" t="s">
+      <c r="AQ1" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="AR1" s="16" t="s">
+      <c r="AR1" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="AS1" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AT1" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="AU1" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="AV1" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="AW1" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX1" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="AY1" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="AZ1" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="BA1" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="BB1" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="BC1" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="BD1" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="BE1" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="BF1" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="BG1" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="BH1" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="BI1" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="BJ1" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="BK1" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="BL1" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="BM1" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="BN1" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="BO1" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="BP1" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="BQ1" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="BR1" s="18" t="s">
-        <v>69</v>
-      </c>
-      <c r="BS1" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="BT1" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="BU1" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="BV1" s="18" t="s">
-        <v>73</v>
-      </c>
-      <c r="BW1" s="18" t="s">
-        <v>74</v>
-      </c>
     </row>
-    <row r="2" spans="1:75">
+    <row r="2" spans="1:44">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="5" t="s">
         <v>4</v>
       </c>
       <c r="F2" s="5" t="s">
@@ -1938,7 +1688,7 @@
       <c r="I2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="J2" s="4" t="s">
         <v>9</v>
       </c>
       <c r="K2" s="4" t="s">
@@ -1959,16 +1709,16 @@
       <c r="P2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="Q2" s="4" t="s">
+      <c r="Q2" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="R2" s="14" t="s">
+      <c r="R2" s="5" t="s">
         <v>17</v>
       </c>
       <c r="S2" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="T2" s="14" t="s">
+      <c r="T2" s="5" t="s">
         <v>19</v>
       </c>
       <c r="U2" s="5" t="s">
@@ -1986,7 +1736,7 @@
       <c r="Y2" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="Z2" s="5" t="s">
+      <c r="Z2" s="14" t="s">
         <v>25</v>
       </c>
       <c r="AA2" s="5" t="s">
@@ -2001,10 +1751,10 @@
       <c r="AD2" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="AE2" s="5" t="s">
+      <c r="AE2" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="AF2" s="5" t="s">
+      <c r="AF2" s="17" t="s">
         <v>31</v>
       </c>
       <c r="AG2" s="5" t="s">
@@ -2013,10 +1763,10 @@
       <c r="AH2" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="AI2" s="5" t="s">
+      <c r="AI2" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="AJ2" s="14" t="s">
+      <c r="AJ2" s="5" t="s">
         <v>35</v>
       </c>
       <c r="AK2" s="5" t="s">
@@ -2037,369 +1787,203 @@
       <c r="AP2" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="AQ2" s="14" t="s">
+      <c r="AQ2" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="AR2" s="17" t="s">
+      <c r="AR2" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="AS2" s="5" t="s">
+    </row>
+    <row r="3" spans="1:37">
+      <c r="A3" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="AT2" s="5" t="s">
+      <c r="B3" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="AU2" s="14" t="s">
+      <c r="C3" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="AV2" s="5" t="s">
+      <c r="D3" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="AW2" s="5" t="s">
+      <c r="E3" s="8"/>
+      <c r="F3" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="AX2" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="AY2" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="AZ2" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="BA2" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="BB2" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="BC2" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="BD2" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="BE2" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="BF2" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="BG2" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="BH2" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="BI2" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="BJ2" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="BK2" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="BL2" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="BM2" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="BN2" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="BO2" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="BP2" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="BQ2" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="BR2" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="BS2" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="BT2" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="BU2" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="BV2" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="BW2" s="5" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="3" spans="1:75">
-      <c r="A3" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="F3" s="8"/>
-      <c r="G3" s="9" t="s">
-        <v>80</v>
-      </c>
+      <c r="G3" s="8"/>
       <c r="H3" s="8"/>
       <c r="I3" s="8"/>
-      <c r="J3" s="8"/>
+      <c r="J3" s="9" t="s">
+        <v>49</v>
+      </c>
       <c r="K3" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="L3" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="M3" s="11" t="s">
-        <v>83</v>
+        <v>50</v>
+      </c>
+      <c r="L3" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="M3" s="9" t="s">
+        <v>52</v>
       </c>
       <c r="N3" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="O3" s="9" t="s">
-        <v>85</v>
+        <v>53</v>
+      </c>
+      <c r="O3" s="12" t="s">
+        <v>54</v>
       </c>
       <c r="P3" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="Q3" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="R3" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="T3" s="15" t="s">
-        <v>89</v>
-      </c>
-      <c r="W3" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="X3" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="Y3" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD3" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="AE3" s="9"/>
+        <v>55</v>
+      </c>
+      <c r="Q3" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="S3" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="T3" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="V3" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="W3" s="9"/>
+      <c r="X3" s="9"/>
+      <c r="Y3" s="9"/>
+      <c r="Z3" s="9"/>
+      <c r="AA3" s="9"/>
+      <c r="AB3" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="AC3" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE3" s="15" t="s">
+        <v>62</v>
+      </c>
       <c r="AF3" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="AG3" s="9"/>
-      <c r="AH3" s="9"/>
-      <c r="AI3" s="9"/>
-      <c r="AJ3" s="9"/>
-      <c r="AK3" s="9"/>
-      <c r="AL3" s="9"/>
-      <c r="AM3" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="AO3" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="AQ3" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="AR3" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="AU3" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="AV3" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="AY3" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="BJ3" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="BK3" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="BL3" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="BU3" s="19" t="s">
-        <v>105</v>
-      </c>
-      <c r="BV3" s="19" t="s">
-        <v>106</v>
-      </c>
-      <c r="BW3" s="19" t="s">
-        <v>107</v>
+        <v>63</v>
+      </c>
+      <c r="AI3" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AJ3" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="AK3" s="12" t="s">
+        <v>66</v>
       </c>
     </row>
-    <row r="4" spans="1:51">
+    <row r="4" spans="1:37">
       <c r="A4" s="7" t="s">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>76</v>
+        <v>45</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="F4" s="8"/>
-      <c r="G4" s="9" t="s">
-        <v>80</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="E4" s="8"/>
+      <c r="F4" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="G4" s="8"/>
       <c r="H4" s="8"/>
       <c r="I4" s="8"/>
-      <c r="J4" s="8"/>
+      <c r="J4" s="9" t="s">
+        <v>49</v>
+      </c>
       <c r="K4" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="L4" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="M4" s="11" t="s">
-        <v>83</v>
+        <v>50</v>
+      </c>
+      <c r="L4" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="M4" s="9" t="s">
+        <v>67</v>
       </c>
       <c r="N4" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="O4" s="9" t="s">
-        <v>85</v>
+        <v>53</v>
+      </c>
+      <c r="O4" s="12" t="s">
+        <v>68</v>
       </c>
       <c r="P4" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="Q4" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="R4" t="s">
-        <v>110</v>
-      </c>
-      <c r="T4" s="15" t="s">
-        <v>89</v>
-      </c>
-      <c r="W4" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="X4" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="Y4" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD4" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="AE4" s="9"/>
+        <v>55</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>69</v>
+      </c>
+      <c r="S4" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="T4" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="V4" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="W4" s="9"/>
+      <c r="X4" s="9"/>
+      <c r="Y4" s="9"/>
+      <c r="Z4" s="9"/>
+      <c r="AA4" s="9"/>
+      <c r="AB4" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="AC4" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE4" s="15" t="s">
+        <v>62</v>
+      </c>
       <c r="AF4" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="AG4" s="9"/>
-      <c r="AH4" s="9"/>
-      <c r="AI4" s="9"/>
-      <c r="AJ4" s="9"/>
-      <c r="AK4" s="9"/>
-      <c r="AL4" s="9"/>
-      <c r="AM4" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="AO4" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="AQ4" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="AR4" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="AU4" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="AV4" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="AY4" s="12" t="s">
-        <v>101</v>
+        <v>63</v>
+      </c>
+      <c r="AI4" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AJ4" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="AK4" s="12" t="s">
+        <v>66</v>
       </c>
     </row>
-    <row r="5" spans="1:51">
+    <row r="5" spans="1:37">
       <c r="A5" s="10" t="s">
-        <v>111</v>
+        <v>70</v>
       </c>
       <c r="B5" s="9"/>
       <c r="C5" s="9"/>
       <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="N5" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="AN5" s="9"/>
-      <c r="AR5" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="AU5" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="AV5" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="AY5" s="9"/>
-    </row>
-    <row r="6" spans="1:51">
-      <c r="A6" s="10"/>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="N6" s="8"/>
-      <c r="AN6" s="9"/>
-      <c r="AR6" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="AV6" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="AY6" s="9"/>
+      <c r="M5" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="AF5" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="AI5" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ5" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="AK5" s="9"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1">
     <cfRule type="duplicateValues" dxfId="0" priority="8"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:BQ1">
+  <conditionalFormatting sqref="A1:AR1">
     <cfRule type="duplicateValues" dxfId="0" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1">
     <cfRule type="duplicateValues" dxfId="0" priority="9"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="BS2">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="BT2">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="BU2:BW2">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A4">
     <cfRule type="duplicateValues" dxfId="0" priority="5"/>
@@ -2413,14 +1997,11 @@
   <conditionalFormatting sqref="B2:B3">
     <cfRule type="duplicateValues" dxfId="0" priority="13"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BE3 AY3 BR4:XFD5 AU3:AV3 AO3:AS3 S3:AM3 A3:Q3 BH3:BT3 S5:AV5 A5:Q5 BX1:XFD3 AY5:BQ5 AR7:AU1048576 AY7:XFD1048576 A2:BR2 R4">
+  <conditionalFormatting sqref="A2:B3 AS$1:XFD$1048576 Q4 AF6:AI1048576 AI3:AK3 R3:AG3 C3:P3 R5:AR5 AK6:AR1048576 AP3 C2:AR2 A5:P5">
     <cfRule type="duplicateValues" dxfId="0" priority="29"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BE4 AY4 BH4:BQ4 AU4:AV4 AO4:AS4 S4:AM4 A4:Q4 R3">
+  <conditionalFormatting sqref="A4:P4 AP4 AI4:AK4 R4:AG4 Q3">
     <cfRule type="duplicateValues" dxfId="0" priority="7"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A6:AV6 AY6:XFD6">
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/utils/reference/bpi_cards_xdays-header.xlsx
+++ b/utils/reference/bpi_cards_xdays-header.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24430"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SPM\XDAYS-AUTOMATION\utils\reference\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19E686B3-91EA-47E2-8955-DB0D563B4B21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11460"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -21,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -30,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="75">
   <si>
     <t>CUST_ID</t>
   </si>
@@ -252,22 +256,20 @@
   </si>
   <si>
     <t>Balance Type (100k up, etc)</t>
+  </si>
+  <si>
+    <t>UnitCode</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="7">
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="0000000000000000"/>
-    <numFmt numFmtId="179" formatCode="#,##0.00\ "/>
-    <numFmt numFmtId="180" formatCode="mm/dd/yyyy"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <numFmts count="2">
+    <numFmt numFmtId="168" formatCode="0000000000000000"/>
+    <numFmt numFmtId="169" formatCode="#,##0.00\ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -283,152 +285,8 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="34">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -447,188 +305,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -636,255 +314,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -906,27 +342,27 @@
     <xf numFmtId="49" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="58" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="58" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -935,59 +371,14 @@
     <xf numFmtId="1" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Link" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="18">
+  <dxfs count="26">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -999,36 +390,233 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
         <color theme="1"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
         <color theme="1"/>
       </font>
       <border>
@@ -1039,7 +627,7 @@
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="0"/>
       </font>
       <fill>
@@ -1067,154 +655,40 @@
           <color theme="4"/>
         </bottom>
         <horizontal style="thin">
-          <color theme="4" tint="0.399975585192419"/>
+          <color theme="4" tint="0.39994506668294322"/>
         </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
       </border>
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="7"/>
-      <tableStyleElement type="headerRow" dxfId="6"/>
-      <tableStyleElement type="totalRow" dxfId="5"/>
-      <tableStyleElement type="firstColumn" dxfId="4"/>
-      <tableStyleElement type="lastColumn" dxfId="3"/>
-      <tableStyleElement type="firstRowStripe" dxfId="2"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="1"/>
+      <tableStyleElement type="wholeTable" dxfId="25"/>
+      <tableStyleElement type="headerRow" dxfId="24"/>
+      <tableStyleElement type="totalRow" dxfId="23"/>
+      <tableStyleElement type="firstColumn" dxfId="22"/>
+      <tableStyleElement type="lastColumn" dxfId="21"/>
+      <tableStyleElement type="firstRowStripe" dxfId="20"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="19"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="17"/>
-      <tableStyleElement type="totalRow" dxfId="16"/>
-      <tableStyleElement type="firstRowStripe" dxfId="15"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="14"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="13"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="11"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="10"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="9"/>
-      <tableStyleElement type="pageFieldValues" dxfId="8"/>
+      <tableStyleElement type="headerRow" dxfId="18"/>
+      <tableStyleElement type="totalRow" dxfId="17"/>
+      <tableStyleElement type="firstRowStripe" dxfId="16"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="15"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="14"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="13"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="12"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="11"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="10"/>
+      <tableStyleElement type="pageFieldValues" dxfId="9"/>
     </tableStyle>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1472,58 +946,58 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AR5"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="8.42857142857143" customWidth="1"/>
-    <col min="2" max="2" width="15.4285714285714" customWidth="1"/>
-    <col min="3" max="3" width="10.5714285714286" customWidth="1"/>
-    <col min="4" max="4" width="9.85714285714286" customWidth="1"/>
-    <col min="5" max="5" width="11.7142857142857" customWidth="1"/>
+    <col min="1" max="1" width="8.42578125" customWidth="1"/>
+    <col min="2" max="2" width="15.42578125" customWidth="1"/>
+    <col min="3" max="3" width="10.5703125" customWidth="1"/>
+    <col min="4" max="4" width="9.85546875" customWidth="1"/>
+    <col min="5" max="5" width="11.7109375" customWidth="1"/>
     <col min="6" max="6" width="10" customWidth="1"/>
     <col min="7" max="7" width="9" customWidth="1"/>
-    <col min="8" max="8" width="6.57142857142857" customWidth="1"/>
-    <col min="9" max="9" width="8.28571428571429" customWidth="1"/>
-    <col min="10" max="10" width="12.8571428571429" customWidth="1"/>
-    <col min="11" max="11" width="23.5714285714286" customWidth="1"/>
-    <col min="12" max="12" width="7.71428571428571" customWidth="1"/>
-    <col min="13" max="13" width="18.8571428571429" customWidth="1"/>
-    <col min="14" max="14" width="18.7142857142857" customWidth="1"/>
-    <col min="15" max="15" width="6.71428571428571" customWidth="1"/>
-    <col min="16" max="16" width="23.7142857142857" customWidth="1"/>
-    <col min="17" max="17" width="20.8571428571429" customWidth="1"/>
-    <col min="18" max="18" width="21.7142857142857" customWidth="1"/>
-    <col min="19" max="19" width="14.8571428571429" customWidth="1"/>
+    <col min="8" max="8" width="6.5703125" customWidth="1"/>
+    <col min="9" max="9" width="8.28515625" customWidth="1"/>
+    <col min="10" max="10" width="12.85546875" customWidth="1"/>
+    <col min="11" max="11" width="23.5703125" customWidth="1"/>
+    <col min="12" max="12" width="7.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.85546875" customWidth="1"/>
+    <col min="14" max="14" width="18.7109375" customWidth="1"/>
+    <col min="15" max="15" width="6.7109375" customWidth="1"/>
+    <col min="16" max="16" width="23.7109375" customWidth="1"/>
+    <col min="17" max="17" width="20.85546875" customWidth="1"/>
+    <col min="18" max="18" width="21.7109375" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" customWidth="1"/>
     <col min="20" max="20" width="28" customWidth="1"/>
-    <col min="21" max="21" width="18.4285714285714" customWidth="1"/>
-    <col min="22" max="22" width="11.2857142857143" customWidth="1"/>
-    <col min="23" max="23" width="4.85714285714286" customWidth="1"/>
-    <col min="24" max="24" width="7.14285714285714" customWidth="1"/>
-    <col min="25" max="25" width="8.71428571428571" customWidth="1"/>
-    <col min="26" max="26" width="10.7142857142857" customWidth="1"/>
-    <col min="27" max="27" width="11.5714285714286" customWidth="1"/>
-    <col min="28" max="28" width="12.8571428571429" customWidth="1"/>
+    <col min="21" max="21" width="18.42578125" customWidth="1"/>
+    <col min="22" max="22" width="11.28515625" customWidth="1"/>
+    <col min="23" max="23" width="4.85546875" customWidth="1"/>
+    <col min="24" max="24" width="7.140625" customWidth="1"/>
+    <col min="25" max="25" width="8.7109375" customWidth="1"/>
+    <col min="26" max="26" width="10.7109375" customWidth="1"/>
+    <col min="27" max="27" width="11.5703125" customWidth="1"/>
+    <col min="28" max="28" width="12.85546875" customWidth="1"/>
     <col min="29" max="30" width="12" customWidth="1"/>
-    <col min="31" max="31" width="12.8571428571429" customWidth="1"/>
-    <col min="32" max="32" width="11.5714285714286" customWidth="1"/>
-    <col min="33" max="33" width="9.28571428571429" customWidth="1"/>
-    <col min="34" max="34" width="18.5714285714286" customWidth="1"/>
+    <col min="31" max="31" width="12.85546875" customWidth="1"/>
+    <col min="32" max="32" width="11.5703125" customWidth="1"/>
+    <col min="33" max="33" width="9.28515625" customWidth="1"/>
+    <col min="34" max="34" width="18.5703125" customWidth="1"/>
     <col min="35" max="35" width="23" customWidth="1"/>
-    <col min="36" max="36" width="25.2857142857143" customWidth="1"/>
-    <col min="37" max="37" width="13.2857142857143" customWidth="1"/>
-    <col min="38" max="38" width="14.5714285714286" customWidth="1"/>
-    <col min="39" max="39" width="15.4285714285714" customWidth="1"/>
-    <col min="40" max="40" width="8.57142857142857" customWidth="1"/>
-    <col min="41" max="41" width="9.28571428571429" customWidth="1"/>
-    <col min="42" max="42" width="9.14285714285714" customWidth="1"/>
-    <col min="43" max="43" width="11.4285714285714" customWidth="1"/>
-    <col min="44" max="44" width="10.5714285714286" customWidth="1"/>
+    <col min="36" max="36" width="25.28515625" customWidth="1"/>
+    <col min="37" max="37" width="13.28515625" customWidth="1"/>
+    <col min="38" max="38" width="14.5703125" customWidth="1"/>
+    <col min="39" max="39" width="15.42578125" customWidth="1"/>
+    <col min="40" max="40" width="8.5703125" customWidth="1"/>
+    <col min="41" max="41" width="9.28515625" customWidth="1"/>
+    <col min="42" max="42" width="9.140625" customWidth="1"/>
+    <col min="43" max="43" width="11.42578125" customWidth="1"/>
+    <col min="44" max="44" width="10.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:44">
@@ -1794,7 +1268,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="3" spans="1:37">
+    <row r="3" spans="1:44">
       <c r="A3" s="7" t="s">
         <v>44</v>
       </c>
@@ -1874,7 +1348,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="4" spans="1:37">
+    <row r="4" spans="1:44">
       <c r="A4" s="7" t="s">
         <v>44</v>
       </c>
@@ -1954,7 +1428,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="5" spans="1:37">
+    <row r="5" spans="1:44">
       <c r="A5" s="10" t="s">
         <v>70</v>
       </c>
@@ -1964,6 +1438,9 @@
       <c r="M5" s="9" t="s">
         <v>71</v>
       </c>
+      <c r="V5" s="18" t="s">
+        <v>74</v>
+      </c>
       <c r="AF5" s="9" t="s">
         <v>72</v>
       </c>
@@ -1977,33 +1454,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1">
-    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:AR1">
-    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1">
-    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A4">
-    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4">
-    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:A3">
-    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:B3">
-    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="13"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:B3 AS$1:XFD$1048576 Q4 AF6:AI1048576 AI3:AK3 R3:AG3 C3:P3 R5:AR5 AK6:AR1048576 AP3 C2:AR2 A5:P5">
-    <cfRule type="duplicateValues" dxfId="0" priority="29"/>
+  <conditionalFormatting sqref="A2:B3 AS1:XFD1048576 Q4 AF6:AI1048576 AI3:AK3 R3:AG3 C3:P3 R5:AR5 AK6:AR1048576 AP3 C2:AR2 A5:P5">
+    <cfRule type="duplicateValues" dxfId="1" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A4:P4 AP4 AI4:AK4 R4:AG4 Q3">
     <cfRule type="duplicateValues" dxfId="0" priority="7"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/utils/reference/bpi_cards_xdays-header.xlsx
+++ b/utils/reference/bpi_cards_xdays-header.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SPM\XDAYS-AUTOMATION\utils\reference\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SPM\Documents\XDAYS-AUTOMATION\utils\reference\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19E686B3-91EA-47E2-8955-DB0D563B4B21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D82A30E3-2D57-41A4-AA15-A22511EC31E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="82">
   <si>
     <t>CUST_ID</t>
   </si>
@@ -259,6 +259,27 @@
   </si>
   <si>
     <t>UnitCode</t>
+  </si>
+  <si>
+    <t>LPA</t>
+  </si>
+  <si>
+    <t>PTP_DATE</t>
+  </si>
+  <si>
+    <t>PTP_AMT</t>
+  </si>
+  <si>
+    <t>LAST_DUE_DATE</t>
+  </si>
+  <si>
+    <t>BALANCE_TYPE</t>
+  </si>
+  <si>
+    <t>BLOCK_CODE</t>
+  </si>
+  <si>
+    <t>HO_FLAG</t>
   </si>
 </sst>
 </file>
@@ -266,8 +287,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="2">
-    <numFmt numFmtId="168" formatCode="0000000000000000"/>
-    <numFmt numFmtId="169" formatCode="#,##0.00\ "/>
+    <numFmt numFmtId="164" formatCode="0000000000000000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00\ "/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -282,7 +303,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -342,15 +363,15 @@
     <xf numFmtId="49" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -952,7 +973,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AR5"/>
+  <dimension ref="A1:AR6"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.42578125" customWidth="1"/>
@@ -1323,7 +1344,9 @@
       </c>
       <c r="W3" s="9"/>
       <c r="X3" s="9"/>
-      <c r="Y3" s="9"/>
+      <c r="Y3" s="9" t="s">
+        <v>81</v>
+      </c>
       <c r="Z3" s="9"/>
       <c r="AA3" s="9"/>
       <c r="AB3" s="9" t="s">
@@ -1337,6 +1360,9 @@
       </c>
       <c r="AF3" s="9" t="s">
         <v>63</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>76</v>
       </c>
       <c r="AI3" s="9" t="s">
         <v>64</v>
@@ -1438,9 +1464,15 @@
       <c r="M5" s="9" t="s">
         <v>71</v>
       </c>
+      <c r="Q5" s="18" t="s">
+        <v>75</v>
+      </c>
       <c r="V5" s="18" t="s">
         <v>74</v>
       </c>
+      <c r="AC5" t="s">
+        <v>80</v>
+      </c>
       <c r="AF5" s="9" t="s">
         <v>72</v>
       </c>
@@ -1450,7 +1482,17 @@
       <c r="AJ5" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="AK5" s="9"/>
+      <c r="AK5" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="6" spans="1:44">
+      <c r="AI6" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="AJ6" s="18" t="s">
+        <v>79</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1">

--- a/utils/reference/bpi_cards_xdays-header.xlsx
+++ b/utils/reference/bpi_cards_xdays-header.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SPM\Documents\XDAYS-AUTOMATION\utils\reference\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D82A30E3-2D57-41A4-AA15-A22511EC31E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C58798BD-F8D7-4F9F-B2FA-0F95CB49AC41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1464,7 +1464,7 @@
       <c r="M5" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="Q5" s="18" t="s">
+      <c r="P5" s="18" t="s">
         <v>75</v>
       </c>
       <c r="V5" s="18" t="s">
@@ -1516,7 +1516,7 @@
   <conditionalFormatting sqref="B2:B3">
     <cfRule type="duplicateValues" dxfId="2" priority="13"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:B3 AS1:XFD1048576 Q4 AF6:AI1048576 AI3:AK3 R3:AG3 C3:P3 R5:AR5 AK6:AR1048576 AP3 C2:AR2 A5:P5">
+  <conditionalFormatting sqref="A2:B3 AS1:XFD1048576 Q4 AF6:AI1048576 AI3:AK3 R3:AG3 C3:P3 R5:AR5 AK6:AR1048576 AP3 C2:AR2 A5:O5">
     <cfRule type="duplicateValues" dxfId="1" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A4:P4 AP4 AI4:AK4 R4:AG4 Q3">

--- a/utils/reference/bpi_cards_xdays-header.xlsx
+++ b/utils/reference/bpi_cards_xdays-header.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SPM\Documents\XDAYS-AUTOMATION\utils\reference\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C58798BD-F8D7-4F9F-B2FA-0F95CB49AC41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA16C029-80D1-429A-9266-9745179A7E5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$AR$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$AS$2</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="85">
   <si>
     <t>CUST_ID</t>
   </si>
@@ -280,6 +280,15 @@
   </si>
   <si>
     <t>HO_FLAG</t>
+  </si>
+  <si>
+    <t>OTHER CONTACT</t>
+  </si>
+  <si>
+    <t>OTHER_CONTACT</t>
+  </si>
+  <si>
+    <t>Other contact</t>
   </si>
 </sst>
 </file>
@@ -973,55 +982,56 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AR6"/>
+  <dimension ref="A1:AS6"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="8.42578125" customWidth="1"/>
+    <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.42578125" customWidth="1"/>
     <col min="3" max="3" width="10.5703125" customWidth="1"/>
     <col min="4" max="4" width="9.85546875" customWidth="1"/>
-    <col min="5" max="5" width="11.7109375" customWidth="1"/>
-    <col min="6" max="6" width="10" customWidth="1"/>
-    <col min="7" max="7" width="9" customWidth="1"/>
-    <col min="8" max="8" width="6.5703125" customWidth="1"/>
-    <col min="9" max="9" width="8.28515625" customWidth="1"/>
-    <col min="10" max="10" width="12.85546875" customWidth="1"/>
-    <col min="11" max="11" width="23.5703125" customWidth="1"/>
-    <col min="12" max="12" width="7.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.85546875" customWidth="1"/>
-    <col min="14" max="14" width="18.7109375" customWidth="1"/>
-    <col min="15" max="15" width="6.7109375" customWidth="1"/>
-    <col min="16" max="16" width="23.7109375" customWidth="1"/>
-    <col min="17" max="17" width="20.85546875" customWidth="1"/>
-    <col min="18" max="18" width="21.7109375" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" customWidth="1"/>
-    <col min="20" max="20" width="28" customWidth="1"/>
-    <col min="21" max="21" width="18.42578125" customWidth="1"/>
-    <col min="22" max="22" width="11.28515625" customWidth="1"/>
-    <col min="23" max="23" width="4.85546875" customWidth="1"/>
-    <col min="24" max="24" width="7.140625" customWidth="1"/>
-    <col min="25" max="25" width="8.7109375" customWidth="1"/>
-    <col min="26" max="26" width="10.7109375" customWidth="1"/>
-    <col min="27" max="27" width="11.5703125" customWidth="1"/>
-    <col min="28" max="28" width="12.85546875" customWidth="1"/>
-    <col min="29" max="30" width="12" customWidth="1"/>
-    <col min="31" max="31" width="12.85546875" customWidth="1"/>
-    <col min="32" max="32" width="11.5703125" customWidth="1"/>
-    <col min="33" max="33" width="9.28515625" customWidth="1"/>
-    <col min="34" max="34" width="18.5703125" customWidth="1"/>
-    <col min="35" max="35" width="23" customWidth="1"/>
-    <col min="36" max="36" width="25.28515625" customWidth="1"/>
-    <col min="37" max="37" width="13.28515625" customWidth="1"/>
-    <col min="38" max="38" width="14.5703125" customWidth="1"/>
-    <col min="39" max="39" width="15.42578125" customWidth="1"/>
-    <col min="40" max="40" width="8.5703125" customWidth="1"/>
-    <col min="41" max="41" width="9.28515625" customWidth="1"/>
-    <col min="42" max="42" width="9.140625" customWidth="1"/>
-    <col min="43" max="43" width="11.42578125" customWidth="1"/>
-    <col min="44" max="44" width="10.5703125" customWidth="1"/>
+    <col min="5" max="6" width="11.7109375" customWidth="1"/>
+    <col min="7" max="7" width="10" customWidth="1"/>
+    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="9" max="9" width="6.5703125" customWidth="1"/>
+    <col min="10" max="10" width="8.28515625" customWidth="1"/>
+    <col min="11" max="11" width="12.85546875" customWidth="1"/>
+    <col min="12" max="12" width="23.5703125" customWidth="1"/>
+    <col min="13" max="13" width="7.7109375" customWidth="1"/>
+    <col min="14" max="14" width="18.85546875" customWidth="1"/>
+    <col min="15" max="15" width="18.7109375" customWidth="1"/>
+    <col min="16" max="16" width="16" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="23.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.85546875" customWidth="1"/>
+    <col min="19" max="19" width="21.7109375" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" customWidth="1"/>
+    <col min="21" max="21" width="28" customWidth="1"/>
+    <col min="22" max="22" width="18.42578125" customWidth="1"/>
+    <col min="23" max="23" width="11.28515625" customWidth="1"/>
+    <col min="24" max="24" width="4.85546875" customWidth="1"/>
+    <col min="25" max="25" width="7.140625" customWidth="1"/>
+    <col min="26" max="26" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="10.7109375" customWidth="1"/>
+    <col min="28" max="28" width="11.5703125" customWidth="1"/>
+    <col min="29" max="29" width="12.85546875" customWidth="1"/>
+    <col min="30" max="30" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12" customWidth="1"/>
+    <col min="32" max="32" width="12.85546875" customWidth="1"/>
+    <col min="33" max="33" width="11.5703125" customWidth="1"/>
+    <col min="34" max="34" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="18.5703125" customWidth="1"/>
+    <col min="36" max="36" width="23" customWidth="1"/>
+    <col min="37" max="37" width="25.28515625" customWidth="1"/>
+    <col min="38" max="38" width="13.28515625" customWidth="1"/>
+    <col min="39" max="39" width="14.5703125" customWidth="1"/>
+    <col min="40" max="40" width="15.42578125" customWidth="1"/>
+    <col min="41" max="41" width="8.5703125" customWidth="1"/>
+    <col min="42" max="42" width="9.28515625" customWidth="1"/>
+    <col min="43" max="43" width="9.140625" customWidth="1"/>
+    <col min="44" max="44" width="11.42578125" customWidth="1"/>
+    <col min="45" max="45" width="10.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44">
+    <row r="1" spans="1:45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1038,124 +1048,127 @@
         <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="13" t="s">
+      <c r="R1" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="S1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="T1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="U1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="V1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="W1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="X1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="Y1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="Z1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="13" t="s">
+      <c r="AA1" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="AB1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="AC1" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AD1" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="2" t="s">
+      <c r="AE1" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="13" t="s">
+      <c r="AF1" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="16" t="s">
+      <c r="AG1" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="2" t="s">
+      <c r="AH1" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="2" t="s">
+      <c r="AI1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="13" t="s">
+      <c r="AJ1" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="2" t="s">
+      <c r="AK1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="2" t="s">
+      <c r="AL1" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" s="2" t="s">
+      <c r="AM1" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="2" t="s">
+      <c r="AN1" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" s="2" t="s">
+      <c r="AO1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="2" t="s">
+      <c r="AP1" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" s="2" t="s">
+      <c r="AQ1" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="AQ1" s="2" t="s">
+      <c r="AR1" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="AR1" s="2" t="s">
+      <c r="AS1" s="2" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:44">
+    <row r="2" spans="1:45">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -1172,124 +1185,127 @@
         <v>4</v>
       </c>
       <c r="F2" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="G2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="H2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="I2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="J2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="K2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="L2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="M2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="N2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="N2" s="4" t="s">
+      <c r="O2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="O2" s="4" t="s">
+      <c r="P2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="P2" s="4" t="s">
+      <c r="Q2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="Q2" s="14" t="s">
+      <c r="R2" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="R2" s="5" t="s">
+      <c r="S2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="S2" s="5" t="s">
+      <c r="T2" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="T2" s="5" t="s">
+      <c r="U2" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="U2" s="5" t="s">
+      <c r="V2" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="V2" s="5" t="s">
+      <c r="W2" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="W2" s="5" t="s">
+      <c r="X2" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="X2" s="5" t="s">
+      <c r="Y2" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="Y2" s="5" t="s">
+      <c r="Z2" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="Z2" s="14" t="s">
+      <c r="AA2" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="AA2" s="5" t="s">
+      <c r="AB2" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="AB2" s="5" t="s">
+      <c r="AC2" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="AC2" s="5" t="s">
+      <c r="AD2" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="AD2" s="5" t="s">
+      <c r="AE2" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="AE2" s="14" t="s">
+      <c r="AF2" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="AF2" s="17" t="s">
+      <c r="AG2" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="AG2" s="5" t="s">
+      <c r="AH2" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="AH2" s="5" t="s">
+      <c r="AI2" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="AI2" s="14" t="s">
+      <c r="AJ2" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="AJ2" s="5" t="s">
+      <c r="AK2" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="AK2" s="5" t="s">
+      <c r="AL2" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="AL2" s="5" t="s">
+      <c r="AM2" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="AM2" s="5" t="s">
+      <c r="AN2" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="AN2" s="5" t="s">
+      <c r="AO2" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="AO2" s="5" t="s">
+      <c r="AP2" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="AP2" s="5" t="s">
+      <c r="AQ2" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="AQ2" s="5" t="s">
+      <c r="AR2" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="AR2" s="5" t="s">
+      <c r="AS2" s="5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="3" spans="1:44">
+    <row r="3" spans="1:45">
       <c r="A3" s="7" t="s">
         <v>44</v>
       </c>
@@ -1303,78 +1319,81 @@
         <v>47</v>
       </c>
       <c r="E3" s="8"/>
-      <c r="F3" s="9" t="s">
+      <c r="F3" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="G3" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="G3" s="8"/>
       <c r="H3" s="8"/>
       <c r="I3" s="8"/>
-      <c r="J3" s="9" t="s">
+      <c r="J3" s="8"/>
+      <c r="K3" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="K3" s="9" t="s">
+      <c r="L3" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="L3" s="11" t="s">
+      <c r="M3" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="M3" s="9" t="s">
+      <c r="N3" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="N3" s="9" t="s">
+      <c r="O3" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="O3" s="12" t="s">
+      <c r="P3" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="P3" s="12" t="s">
+      <c r="Q3" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="Q3" s="15" t="s">
+      <c r="R3" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="S3" s="9" t="s">
+      <c r="T3" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="T3" s="9" t="s">
+      <c r="U3" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="V3" s="9" t="s">
+      <c r="W3" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="W3" s="9"/>
       <c r="X3" s="9"/>
-      <c r="Y3" s="9" t="s">
+      <c r="Y3" s="9"/>
+      <c r="Z3" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="Z3" s="9"/>
       <c r="AA3" s="9"/>
-      <c r="AB3" s="9" t="s">
+      <c r="AB3" s="9"/>
+      <c r="AC3" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="AC3" s="9" t="s">
+      <c r="AD3" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="AE3" s="15" t="s">
+      <c r="AF3" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="AF3" s="9" t="s">
+      <c r="AG3" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="AG3" t="s">
+      <c r="AH3" t="s">
         <v>76</v>
       </c>
-      <c r="AI3" s="9" t="s">
+      <c r="AJ3" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="AJ3" s="9" t="s">
+      <c r="AK3" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="AK3" s="12" t="s">
+      <c r="AL3" s="12" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="4" spans="1:44">
+    <row r="4" spans="1:45">
       <c r="A4" s="7" t="s">
         <v>44</v>
       </c>
@@ -1388,109 +1407,110 @@
         <v>47</v>
       </c>
       <c r="E4" s="8"/>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="8"/>
+      <c r="G4" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="G4" s="8"/>
       <c r="H4" s="8"/>
       <c r="I4" s="8"/>
-      <c r="J4" s="9" t="s">
+      <c r="J4" s="8"/>
+      <c r="K4" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="K4" s="9" t="s">
+      <c r="L4" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="L4" s="11" t="s">
+      <c r="M4" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="M4" s="9" t="s">
+      <c r="N4" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="N4" s="9" t="s">
+      <c r="O4" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="O4" s="12" t="s">
+      <c r="P4" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="P4" s="12" t="s">
+      <c r="Q4" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="Q4" t="s">
+      <c r="R4" t="s">
         <v>69</v>
       </c>
-      <c r="S4" s="9" t="s">
+      <c r="T4" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="T4" s="9" t="s">
+      <c r="U4" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="V4" s="9" t="s">
+      <c r="W4" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="W4" s="9"/>
       <c r="X4" s="9"/>
       <c r="Y4" s="9"/>
       <c r="Z4" s="9"/>
       <c r="AA4" s="9"/>
-      <c r="AB4" s="9" t="s">
+      <c r="AB4" s="9"/>
+      <c r="AC4" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="AC4" s="9" t="s">
+      <c r="AD4" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="AE4" s="15" t="s">
+      <c r="AF4" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="AF4" s="9" t="s">
+      <c r="AG4" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="AI4" s="9" t="s">
+      <c r="AJ4" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="AJ4" s="9" t="s">
+      <c r="AK4" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="AK4" s="12" t="s">
+      <c r="AL4" s="12" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="5" spans="1:44">
+    <row r="5" spans="1:45">
       <c r="A5" s="10" t="s">
         <v>70</v>
       </c>
       <c r="B5" s="9"/>
       <c r="C5" s="9"/>
       <c r="D5" s="9"/>
-      <c r="M5" s="9" t="s">
+      <c r="N5" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="P5" s="18" t="s">
+      <c r="Q5" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="V5" s="18" t="s">
+      <c r="W5" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="AC5" t="s">
+      <c r="AD5" t="s">
         <v>80</v>
       </c>
-      <c r="AF5" s="9" t="s">
+      <c r="AG5" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="AI5" s="9" t="s">
+      <c r="AJ5" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="AJ5" s="9" t="s">
+      <c r="AK5" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="AK5" s="9" t="s">
+      <c r="AL5" s="9" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="6" spans="1:44">
-      <c r="AI6" s="18" t="s">
+    <row r="6" spans="1:45">
+      <c r="AJ6" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="AJ6" s="18" t="s">
+      <c r="AK6" s="18" t="s">
         <v>79</v>
       </c>
     </row>
@@ -1498,7 +1518,7 @@
   <conditionalFormatting sqref="A1">
     <cfRule type="duplicateValues" dxfId="8" priority="8"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:AR1">
+  <conditionalFormatting sqref="A1:AS1">
     <cfRule type="duplicateValues" dxfId="7" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1">
@@ -1516,10 +1536,10 @@
   <conditionalFormatting sqref="B2:B3">
     <cfRule type="duplicateValues" dxfId="2" priority="13"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:B3 AS1:XFD1048576 Q4 AF6:AI1048576 AI3:AK3 R3:AG3 C3:P3 R5:AR5 AK6:AR1048576 AP3 C2:AR2 A5:O5">
+  <conditionalFormatting sqref="AT1:XFD1048576 A2:B3 R4 AG6:AJ1048576 AJ3:AL3 S3:AH3 C3:Q3 S5:AS5 AL6:AS1048576 AQ3 C2:AS2 A5:P5">
     <cfRule type="duplicateValues" dxfId="1" priority="29"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A4:P4 AP4 AI4:AK4 R4:AG4 Q3">
+  <conditionalFormatting sqref="A4:Q4 AQ4 AJ4:AL4 S4:AH4 R3">
     <cfRule type="duplicateValues" dxfId="0" priority="7"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
